--- a/data/trans_orig/IP07C19-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C19-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>26474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36681</t>
+          <t>36583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>27399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57179</t>
+          <t>57210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37844</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30006</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135369</t>
+          <t>135371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152958</t>
+          <t>153834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162722</t>
+          <t>161645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>181372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304317</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331108</t>
+          <t>330834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40382</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>67151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82056</t>
+          <t>81802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>35214</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55641</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>57842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>204744</t>
+          <t>204648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>228519</t>
+          <t>227497</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>229238</t>
+          <t>229304</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>252661</t>
+          <t>251674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>440002</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>472974</t>
+          <t>473442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>39357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33709</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>53879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69409</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>26302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33757</t>
+          <t>33883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54811</t>
+          <t>54859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>31816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54354</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39375</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>109213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131112</t>
+          <t>132024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136711</t>
+          <t>135808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159280</t>
+          <t>158899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252692</t>
+          <t>252844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284220</t>
+          <t>286215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25925</t>
+          <t>26160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>27390</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64110</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,03%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>42685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>65996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41984</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79718</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>47809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,82 +6092,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>44248</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>34761</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>56285</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>81005</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>67453</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>96516</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>15,17%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>44248</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>34467</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>54612</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>81005</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>68065</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>94895</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>179607</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>208362</t>
+          <t>208522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>194478</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>222868</t>
+          <t>223899</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>385962</t>
+          <t>383675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>423736</t>
+          <t>424157</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>26275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>52290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25604</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>38036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>42122</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>37885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58275</t>
+          <t>58413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61205</t>
+          <t>60958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83208</t>
+          <t>82732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112271</t>
+          <t>112702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152459</t>
+          <t>152697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176540</t>
+          <t>177581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131046</t>
+          <t>130935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156536</t>
+          <t>156182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290964</t>
+          <t>290959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325790</t>
+          <t>327440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>45848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>44873</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58472</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102666</t>
+          <t>102028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55273</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>59438</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55409</t>
+          <t>55552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79304</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>118137</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151282</t>
+          <t>152509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>211873</t>
+          <t>213935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240816</t>
+          <t>242492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>205872</t>
+          <t>203686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>235914</t>
+          <t>233569</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>425035</t>
+          <t>427904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>466564</t>
+          <t>469233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43135</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129797</t>
+          <t>129348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147509</t>
+          <t>148621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164888</t>
+          <t>163082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186980</t>
+          <t>187259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300441</t>
+          <t>302034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330460</t>
+          <t>330833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>37859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49018</t>
+          <t>49412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74279</t>
+          <t>73901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86012</t>
+          <t>85571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55357</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177918</t>
+          <t>177783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195923</t>
+          <t>195899</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>221063</t>
+          <t>223606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>247439</t>
+          <t>247473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>406842</t>
+          <t>406394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>439575</t>
+          <t>438341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
